--- a/04_DESIGN_TABLES/DesignTable_6807.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6807.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -636,7 +641,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6807-06-06 NWO-FG</t>
+          <t>6807-06-06-NWO-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -668,7 +673,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>6807-06-06 NWO-FG</t>
+          <t>6807-06-06-NWO-FG</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -684,6 +689,11 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>Air-Way s140 only (double-pass 12 rows)</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>renamed from Air-Way "6807-06-06 NWO-FG" to the OMi part number (2026-10-18)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1418,6 +1428,154 @@
       <c r="Q18" t="inlineStr">
         <is>
           <t>6807-12-12-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6807-16-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>6807-16-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (B (1) UN/UNF-2A) x 1 5/16-12 (B (2) UN/UNF-2A)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / locknut hexes / flats / bores from the Brennan TFA catalog p.44; ORB majors from the end library</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.44 alone; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>6807-16-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6807-20-20-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>6807-20-20-NWO-FG</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (B (1) UN/UNF-2A) x 1 5/8-12 (B (2) UN/UNF-2A)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / locknut hexes / flats / bores from the Brennan TFA catalog p.44; ORB majors from the end library</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.44 alone; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>6807-20-20-NWO-FG</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_6807.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6807.xlsx
@@ -1476,17 +1476,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / locknut hexes / flats / bores from the Brennan TFA catalog p.44; ORB majors from the end library</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / locknut hexes / flats / bores from the Brennan TFA catalog p.44; ORB majors from the end library | 2026-10-20 (batch 19 D_geom): DataStatus MISSING -&gt; ASSUMED - one source (Brennan TFA catalog p.44 TFA-p044-t01); generated with the batch-17 6807 SPEC</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.44 alone; marked DimSource BRENNAN</t>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.44 alone; marked DimSource BRENNAN | 2026-10-20: DataStatus MISSING -&gt; ASSUMED (Brennan catalog only; 1504 / 6807 SPEC exists since batch 17)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / locknut hexes / flats / bores from the Brennan TFA catalog p.44; ORB majors from the end library</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / locknut hexes / flats / bores from the Brennan TFA catalog p.44; ORB majors from the end library | 2026-10-20 (batch 19 D_geom): DataStatus MISSING -&gt; ASSUMED - one source (Brennan TFA catalog p.44 TFA-p044-t01); generated with the batch-17 6807 SPEC</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.44 alone; marked DimSource BRENNAN</t>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.44 alone; marked DimSource BRENNAN | 2026-10-20: DataStatus MISSING -&gt; ASSUMED (Brennan catalog only; 1504 / 6807 SPEC exists since batch 17)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
